--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>226089</t>
+          <t>226089 $\pm$ 0.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>213894</t>
+          <t>213894 $\pm$ 0.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>207620</t>
+          <t>207620 $\pm$ 0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>203429</t>
+          <t>203429 $\pm$ 0.00</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>222839</t>
+          <t>222839 $\pm$ 472122.94</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>171981</t>
+          <t>171981 $\pm$ 752331.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>140523</t>
+          <t>140523 $\pm$ 1035136.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>118188</t>
+          <t>118188 $\pm$ 1137432.96</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>222283</t>
+          <t>222283 $\pm$ 457555.72</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>169300</t>
+          <t>169300 $\pm$ 640906.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>136671</t>
+          <t>136671 $\pm$ 813603.90</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>113543</t>
+          <t>113543 $\pm$ 850454.77</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220086</t>
+          <t>220086 $\pm$ 628761.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>161349</t>
+          <t>161349 $\pm$ 1437581.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>130896</t>
+          <t>130896 $\pm$ 2792420.94</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>113393</t>
+          <t>113393 $\pm$ 3839473.44</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>218509</t>
+          <t>218509 $\pm$ 669930.19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>155989</t>
+          <t>155989 $\pm$ 1886652.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121859</t>
+          <t>121859 $\pm$ 2875477.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>99987</t>
+          <t>99987 $\pm$ 3229487.34</t>
         </is>
       </c>
     </row>

--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>226089 $\pm$ 0.00</t>
+          <t>219706 $\pm$ 257</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>213894 $\pm$ 0.00</t>
+          <t>213894 $\pm$ 0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>207620 $\pm$ 0.00</t>
+          <t>207620 $\pm$ 0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>203429 $\pm$ 0.00</t>
+          <t>203429 $\pm$ 0</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>222839 $\pm$ 472122.94</t>
+          <t>214788 $\pm$ 1464</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>171981 $\pm$ 752331.66</t>
+          <t>165102 $\pm$ 0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>140523 $\pm$ 1035136.32</t>
+          <t>129945 $\pm$ 0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>118188 $\pm$ 1137432.96</t>
+          <t>104928 $\pm$ 0</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>222283 $\pm$ 457555.72</t>
+          <t>213908 $\pm$ 1455</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>169300 $\pm$ 640906.85</t>
+          <t>162535 $\pm$ 0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>136671 $\pm$ 813603.90</t>
+          <t>126469 $\pm$ 0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>113543 $\pm$ 850454.77</t>
+          <t>100936 $\pm$ 0</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220086 $\pm$ 628761.50</t>
+          <t>210471 $\pm$ 1773</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>161349 $\pm$ 1437581.02</t>
+          <t>154251 $\pm$ 0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>130896 $\pm$ 2792420.94</t>
+          <t>120459 $\pm$ 0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>113393 $\pm$ 3839473.44</t>
+          <t>101116 $\pm$ 0</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>218509 $\pm$ 669930.19</t>
+          <t>208363 $\pm$ 1961</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>155989 $\pm$ 1886652.94</t>
+          <t>147491 $\pm$ 0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121859 $\pm$ 2875477.12</t>
+          <t>109373 $\pm$ 0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>99987 $\pm$ 3229487.34</t>
+          <t>85426 $\pm$ 0</t>
         </is>
       </c>
     </row>

--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -1,43 +1,149 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\phd\05_multi_performative_stable\multiplayer-performative-stable\ride_share\figs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE24B37-ECA9-47F7-9894-D9CC5C104A08}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>$\mu_A$=0.25</t>
+  </si>
+  <si>
+    <t>$\mu_A$=0.5</t>
+  </si>
+  <si>
+    <t>$\mu_A$=0.75</t>
+  </si>
+  <si>
+    <t>$\mu_A$=1.0</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>224556 $\pm$ 1186</t>
+  </si>
+  <si>
+    <t>217440 $\pm$ 834</t>
+  </si>
+  <si>
+    <t>214132 $\pm$ 1503</t>
+  </si>
+  <si>
+    <t>210790 $\pm$ 1336</t>
+  </si>
+  <si>
+    <t>RGD</t>
+  </si>
+  <si>
+    <t>176232 $\pm$ 4046</t>
+  </si>
+  <si>
+    <t>99141 $\pm$ 2923</t>
+  </si>
+  <si>
+    <t>65041 $\pm$ 2262</t>
+  </si>
+  <si>
+    <t>45986 $\pm$ 1860</t>
+  </si>
+  <si>
+    <t>SFB</t>
+  </si>
+  <si>
+    <t>212102 $\pm$ 3375</t>
+  </si>
+  <si>
+    <t>157131 $\pm$ 4805</t>
+  </si>
+  <si>
+    <t>118173 $\pm$ 4942</t>
+  </si>
+  <si>
+    <t>92016 $\pm$ 4990</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>186364 $\pm$ 2964</t>
+  </si>
+  <si>
+    <t>148872 $\pm$ 5652</t>
+  </si>
+  <si>
+    <t>151494 $\pm$ 9386</t>
+  </si>
+  <si>
+    <t>157927 $\pm$ 9953</t>
+  </si>
+  <si>
+    <t>OPGD</t>
+  </si>
+  <si>
+    <t>160929 $\pm$ 2007</t>
+  </si>
+  <si>
+    <t>129170 $\pm$ 2337</t>
+  </si>
+  <si>
+    <t>117443 $\pm$ 1806</t>
+  </si>
+  <si>
+    <t>113418 $\pm$ 1453</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -46,93 +152,99 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,177 +532,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$=0.25</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$=0.5</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$=0.75</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$=1.0</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>219706 $\pm$ 257</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>213894 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>207620 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>203429 $\pm$ 0</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>RGD</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>214788 $\pm$ 1464</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>165102 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>129945 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>104928 $\pm$ 0</t>
-        </is>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SFB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>213908 $\pm$ 1455</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>162535 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>126469 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100936 $\pm$ 0</t>
-        </is>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>210471 $\pm$ 1773</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>154251 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>120459 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>101116 $\pm$ 0</t>
-        </is>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OPGD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>208363 $\pm$ 1961</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>147491 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>109373 $\pm$ 0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>85426 $\pm$ 0</t>
-        </is>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -1,149 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\phd\05_multi_performative_stable\multiplayer-performative-stable\ride_share\figs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE24B37-ECA9-47F7-9894-D9CC5C104A08}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>$\mu_A$=0.25</t>
-  </si>
-  <si>
-    <t>$\mu_A$=0.5</t>
-  </si>
-  <si>
-    <t>$\mu_A$=0.75</t>
-  </si>
-  <si>
-    <t>$\mu_A$=1.0</t>
-  </si>
-  <si>
-    <t>RR</t>
-  </si>
-  <si>
-    <t>224556 $\pm$ 1186</t>
-  </si>
-  <si>
-    <t>217440 $\pm$ 834</t>
-  </si>
-  <si>
-    <t>214132 $\pm$ 1503</t>
-  </si>
-  <si>
-    <t>210790 $\pm$ 1336</t>
-  </si>
-  <si>
-    <t>RGD</t>
-  </si>
-  <si>
-    <t>176232 $\pm$ 4046</t>
-  </si>
-  <si>
-    <t>99141 $\pm$ 2923</t>
-  </si>
-  <si>
-    <t>65041 $\pm$ 2262</t>
-  </si>
-  <si>
-    <t>45986 $\pm$ 1860</t>
-  </si>
-  <si>
-    <t>SFB</t>
-  </si>
-  <si>
-    <t>212102 $\pm$ 3375</t>
-  </si>
-  <si>
-    <t>157131 $\pm$ 4805</t>
-  </si>
-  <si>
-    <t>118173 $\pm$ 4942</t>
-  </si>
-  <si>
-    <t>92016 $\pm$ 4990</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>186364 $\pm$ 2964</t>
-  </si>
-  <si>
-    <t>148872 $\pm$ 5652</t>
-  </si>
-  <si>
-    <t>151494 $\pm$ 9386</t>
-  </si>
-  <si>
-    <t>157927 $\pm$ 9953</t>
-  </si>
-  <si>
-    <t>OPGD</t>
-  </si>
-  <si>
-    <t>160929 $\pm$ 2007</t>
-  </si>
-  <si>
-    <t>129170 $\pm$ 2337</t>
-  </si>
-  <si>
-    <t>117443 $\pm$ 1806</t>
-  </si>
-  <si>
-    <t>113418 $\pm$ 1453</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -152,99 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -532,112 +420,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5"/>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.25</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.75</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 1.0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>224556 $\pm$ 1186</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>217440 $\pm$ 834</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>214132 $\pm$ 1503</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>210790 $\pm$ 1336</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RGD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>176232 $\pm$ 4046</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>99141 $\pm$ 2923</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>65041 $\pm$ 2262</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45986 $\pm$ 1860</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SFB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>212102 $\pm$ 3375</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>157131 $\pm$ 4805</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>118173 $\pm$ 4942</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>92016 $\pm$ 4990</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>186364 $\pm$ 2964</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>148872 $\pm$ 5652</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>151494 $\pm$ 9386</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>157927 $\pm$ 9953</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OPGD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160929 $\pm$ 2007</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>129170 $\pm$ 2337</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>117443 $\pm$ 1806</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>113418 $\pm$ 1453</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>SIR$^2$</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>224556 $\pm$ 1186</t>
+          <t>228348 $\pm$ 664</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>217440 $\pm$ 834</t>
+          <t>219390 $\pm$ 723</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>214132 $\pm$ 1503</t>
+          <t>217054 $\pm$ 954</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>210790 $\pm$ 1336</t>
+          <t>214854 $\pm$ 780</t>
         </is>
       </c>
     </row>

--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -1,43 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\phd\05_multiplayer_performative_stable\multiplayer-performative-stable\ride_share\figs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC0781C-1DBB-4A77-8F10-EFFC4DD712B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>$\mu_A$ = 0.25</t>
+  </si>
+  <si>
+    <t>$\mu_A$ = 0.5</t>
+  </si>
+  <si>
+    <t>$\mu_A$ = 0.75</t>
+  </si>
+  <si>
+    <t>$\mu_A$ = 1.0</t>
+  </si>
+  <si>
+    <t>SIR$^2$</t>
+  </si>
+  <si>
+    <t>228348 $\pm$ 664</t>
+  </si>
+  <si>
+    <t>219390 $\pm$ 723</t>
+  </si>
+  <si>
+    <t>217054 $\pm$ 954</t>
+  </si>
+  <si>
+    <t>214854 $\pm$ 780</t>
+  </si>
+  <si>
+    <t>RGD</t>
+  </si>
+  <si>
+    <t>176232 $\pm$ 4046</t>
+  </si>
+  <si>
+    <t>99141 $\pm$ 2923</t>
+  </si>
+  <si>
+    <t>65041 $\pm$ 2262</t>
+  </si>
+  <si>
+    <t>45986 $\pm$ 1860</t>
+  </si>
+  <si>
+    <t>SFB</t>
+  </si>
+  <si>
+    <t>212102 $\pm$ 3375</t>
+  </si>
+  <si>
+    <t>157131 $\pm$ 4805</t>
+  </si>
+  <si>
+    <t>118173 $\pm$ 4942</t>
+  </si>
+  <si>
+    <t>92016 $\pm$ 4990</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>186364 $\pm$ 2964</t>
+  </si>
+  <si>
+    <t>148872 $\pm$ 5652</t>
+  </si>
+  <si>
+    <t>151494 $\pm$ 9386</t>
+  </si>
+  <si>
+    <t>157927 $\pm$ 9953</t>
+  </si>
+  <si>
+    <t>OPGD</t>
+  </si>
+  <si>
+    <t>160929 $\pm$ 2007</t>
+  </si>
+  <si>
+    <t>129170 $\pm$ 2337</t>
+  </si>
+  <si>
+    <t>117443 $\pm$ 1806</t>
+  </si>
+  <si>
+    <t>113418 $\pm$ 1453</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -46,93 +155,99 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,177 +535,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="8.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$ = 0.25</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$ = 0.5</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$ = 0.75</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>$\mu_A$ = 1.0</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>SIR$^2$</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>228348 $\pm$ 664</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>219390 $\pm$ 723</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>217054 $\pm$ 954</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>214854 $\pm$ 780</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>RGD</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>176232 $\pm$ 4046</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>99141 $\pm$ 2923</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>65041 $\pm$ 2262</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>45986 $\pm$ 1860</t>
-        </is>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SFB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>212102 $\pm$ 3375</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>157131 $\pm$ 4805</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>118173 $\pm$ 4942</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>92016 $\pm$ 4990</t>
-        </is>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>186364 $\pm$ 2964</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>148872 $\pm$ 5652</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>151494 $\pm$ 9386</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>157927 $\pm$ 9953</t>
-        </is>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OPGD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160929 $\pm$ 2007</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>129170 $\pm$ 2337</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>117443 $\pm$ 1806</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>113418 $\pm$ 1453</t>
-        </is>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -1,152 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\phd\05_multiplayer_performative_stable\multiplayer-performative-stable\ride_share\figs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC0781C-1DBB-4A77-8F10-EFFC4DD712B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>$\mu_A$ = 0.25</t>
-  </si>
-  <si>
-    <t>$\mu_A$ = 0.5</t>
-  </si>
-  <si>
-    <t>$\mu_A$ = 0.75</t>
-  </si>
-  <si>
-    <t>$\mu_A$ = 1.0</t>
-  </si>
-  <si>
-    <t>SIR$^2$</t>
-  </si>
-  <si>
-    <t>228348 $\pm$ 664</t>
-  </si>
-  <si>
-    <t>219390 $\pm$ 723</t>
-  </si>
-  <si>
-    <t>217054 $\pm$ 954</t>
-  </si>
-  <si>
-    <t>214854 $\pm$ 780</t>
-  </si>
-  <si>
-    <t>RGD</t>
-  </si>
-  <si>
-    <t>176232 $\pm$ 4046</t>
-  </si>
-  <si>
-    <t>99141 $\pm$ 2923</t>
-  </si>
-  <si>
-    <t>65041 $\pm$ 2262</t>
-  </si>
-  <si>
-    <t>45986 $\pm$ 1860</t>
-  </si>
-  <si>
-    <t>SFB</t>
-  </si>
-  <si>
-    <t>212102 $\pm$ 3375</t>
-  </si>
-  <si>
-    <t>157131 $\pm$ 4805</t>
-  </si>
-  <si>
-    <t>118173 $\pm$ 4942</t>
-  </si>
-  <si>
-    <t>92016 $\pm$ 4990</t>
-  </si>
-  <si>
-    <t>AGM</t>
-  </si>
-  <si>
-    <t>186364 $\pm$ 2964</t>
-  </si>
-  <si>
-    <t>148872 $\pm$ 5652</t>
-  </si>
-  <si>
-    <t>151494 $\pm$ 9386</t>
-  </si>
-  <si>
-    <t>157927 $\pm$ 9953</t>
-  </si>
-  <si>
-    <t>OPGD</t>
-  </si>
-  <si>
-    <t>160929 $\pm$ 2007</t>
-  </si>
-  <si>
-    <t>129170 $\pm$ 2337</t>
-  </si>
-  <si>
-    <t>117443 $\pm$ 1806</t>
-  </si>
-  <si>
-    <t>113418 $\pm$ 1453</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -155,99 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -535,115 +420,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="8.7265625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.25</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 0.75</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>$\mu_A$ = 1.0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SIR$^2$</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>228348 $\pm$ 664</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>219390 $\pm$ 723</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>217054 $\pm$ 954</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>214854 $\pm$ 780</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RGD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>176232 $\pm$ 4046</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>99141 $\pm$ 2923</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>65041 $\pm$ 2262</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45986 $\pm$ 1860</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SFB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>212102 $\pm$ 3375</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>157131 $\pm$ 4805</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>118173 $\pm$ 4942</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>92016 $\pm$ 4990</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>186364 $\pm$ 2964</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>148872 $\pm$ 5652</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>151494 $\pm$ 9386</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>157927 $\pm$ 9953</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OPGD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160929 $\pm$ 2007</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>129170 $\pm$ 2337</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>117443 $\pm$ 1806</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>113418 $\pm$ 1453</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ride_share/figs/total_revenue.xlsx
+++ b/ride_share/figs/total_revenue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,108 +485,135 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>RGD</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>176232 $\pm$ 4046</t>
+          <t>207515 $\pm$ 2713</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>99141 $\pm$ 2923</t>
+          <t>135764 $\pm$ 4790</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>65041 $\pm$ 2262</t>
+          <t>84074 $\pm$ 5266</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45986 $\pm$ 1860</t>
+          <t>49624 $\pm$ 3890</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SFB</t>
+          <t>RGD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>212102 $\pm$ 3375</t>
+          <t>176234 $\pm$ 4046</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>157131 $\pm$ 4805</t>
+          <t>99144 $\pm$ 2923</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>118173 $\pm$ 4942</t>
+          <t>65043 $\pm$ 2262</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>92016 $\pm$ 4990</t>
+          <t>45988 $\pm$ 1860</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>SFB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>186364 $\pm$ 2964</t>
+          <t>212100 $\pm$ 3375</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>148872 $\pm$ 5652</t>
+          <t>157129 $\pm$ 4805</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>151494 $\pm$ 9386</t>
+          <t>118171 $\pm$ 4942</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>157927 $\pm$ 9953</t>
+          <t>92014 $\pm$ 4990</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>AGM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>197238 $\pm$ 2105</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>165073 $\pm$ 3677</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>156931 $\pm$ 6651</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>160432 $\pm$ 9199</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>OPGD</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160929 $\pm$ 2007</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>129170 $\pm$ 2337</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>117443 $\pm$ 1806</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>113418 $\pm$ 1453</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>154892 $\pm$ 1911</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>123970 $\pm$ 2029</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>116652 $\pm$ 2331</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>113742 $\pm$ 2767</t>
         </is>
       </c>
     </row>
